--- a/data/computational_data_processed/quencher_properties_ml.xlsx
+++ b/data/computational_data_processed/quencher_properties_ml.xlsx
@@ -470,10 +470,10 @@
     <col width="2" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="37" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -529,22 +529,22 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>lambda_S_T / kcal mol-1</t>
+          <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>lambda_S_T_uncertainty / kcal mol-1</t>
+          <t>lambda_S0_T1_uncertainty / kcal mol-1</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>lambda_T_S / kcal mol-1</t>
+          <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>lambda_T_S_uncertainty / kcal mol-1</t>
+          <t>lambda_T1_S0_uncertainty / kcal mol-1</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>lambda_S_T / kcal mol-1</t>
+          <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Singlet-surface reorganization energy, the model's counterpart to the DFT lambda_S_T.</t>
+          <t>S0 surface: E_S0 at the T1 geometry minus E_S0 at its own. The model's counterpart to the DFT lambda_S0_T1.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>lambda_S_T_uncertainty / kcal mol-1</t>
+          <t>lambda_S0_T1_uncertainty / kcal mol-1</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>lambda_T_S / kcal mol-1</t>
+          <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Triplet-surface reorganization energy, the model's counterpart to the DFT lambda_T_S.</t>
+          <t>T1 surface: E_T1 at the S0 geometry minus E_T1 at its own. The model's counterpart to the DFT lambda_T1_S0.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>lambda_T_S_uncertainty / kcal mol-1</t>
+          <t>lambda_T1_S0_uncertainty / kcal mol-1</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">

--- a/data/computational_data_processed/quencher_properties_ml.xlsx
+++ b/data/computational_data_processed/quencher_properties_ml.xlsx
@@ -568,22 +568,22 @@
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>60.0925</v>
+        <v>60.09</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1.41276</v>
+        <v>1.41</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>13.3301</v>
+        <v>13.33</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1.15484</v>
+        <v>1.15</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.0269</v>
+        <v>12.03</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.1953</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>53.2761</v>
+        <v>53.28</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.29527</v>
+        <v>2.3</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>81.075</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>22.698</v>
+        <v>22.7</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>23.1696</v>
+        <v>23.17</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>4.55577</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="5">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>60.7243</v>
+        <v>60.72</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.67012</v>
+        <v>1.67</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>32.4633</v>
+        <v>32.46</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>3.08594</v>
+        <v>3.09</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>19.177</v>
+        <v>19.18</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>2.82006</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="6">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>67.5737</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1.24758</v>
+        <v>1.25</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>15.4268</v>
+        <v>15.43</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2.11783</v>
+        <v>2.12</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>11.5211</v>
+        <v>11.52</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>1.34125</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="7">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>58.5243</v>
+        <v>58.52</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2.61564</v>
+        <v>2.62</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>11.7875</v>
+        <v>11.79</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1.48158</v>
+        <v>1.48</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>10.1995</v>
+        <v>10.2</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>1.69834</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60.4821</v>
+        <v>60.48</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1.38441</v>
+        <v>1.38</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>13.4445</v>
+        <v>13.44</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1.0805</v>
+        <v>1.08</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>11.3976</v>
+        <v>11.4</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>1.64012</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>59.7403</v>
+        <v>59.74</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.6379</v>
+        <v>1.64</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.0587</v>
+        <v>11.06</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.2919</v>
+        <v>1.29</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.141959999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.02317</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="10">
@@ -834,22 +834,22 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>47.0205</v>
+        <v>47.02</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2.83028</v>
+        <v>2.83</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>58.4731</v>
+        <v>58.47</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>5.03024</v>
+        <v>5.03</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>31.473</v>
+        <v>31.47</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.58298</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="11">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>57.016</v>
+        <v>57.02</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2.26207</v>
+        <v>2.26</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>17.5343</v>
+        <v>17.53</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>2.13736</v>
+        <v>2.14</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>13.3314</v>
+        <v>13.33</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.95216</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="12">
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>72.20310000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2.91969</v>
+        <v>2.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>28.6437</v>
+        <v>28.64</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>8.72418</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>13.7299</v>
+        <v>13.73</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.81368</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="13">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>75.5955</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.75512</v>
+        <v>4.76</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28.8662</v>
+        <v>28.87</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>10.5902</v>
+        <v>10.59</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>17.3372</v>
+        <v>17.34</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.36233</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="14">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>53.3311</v>
+        <v>53.33</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3.93554</v>
+        <v>3.94</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>21.0781</v>
+        <v>21.08</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>5.86284</v>
+        <v>5.86</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.2703</v>
+        <v>17.27</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3.58703</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="15">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>57.0497</v>
+        <v>57.05</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3.50016</v>
+        <v>3.5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>19.0453</v>
+        <v>19.05</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>2.97534</v>
+        <v>2.98</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>14.4819</v>
+        <v>14.48</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1.64722</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>53.8298</v>
+        <v>53.83</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2.21181</v>
+        <v>2.21</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>91.5772</v>
+        <v>91.58</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>9.142300000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>29.9049</v>
+        <v>29.9</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>5.1007</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="17">
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>61.2325</v>
+        <v>61.23</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3.05818</v>
+        <v>3.06</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>17.1394</v>
+        <v>17.14</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1.99567</v>
+        <v>2</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>14.1105</v>
+        <v>14.11</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.52664</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="18">
@@ -1138,22 +1138,22 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>56.7799</v>
+        <v>56.78</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1.95314</v>
+        <v>1.95</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>11.0327</v>
+        <v>11.03</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1.33435</v>
+        <v>1.33</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>9.46231</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.935717</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>79.85720000000001</v>
+        <v>79.86</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1.92007</v>
+        <v>1.92</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19.6409</v>
+        <v>19.64</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>9.78716</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>12.6203</v>
+        <v>12.62</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>4.01696</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="20">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>54.5922</v>
+        <v>54.59</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2.87584</v>
+        <v>2.88</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>23.5737</v>
+        <v>23.57</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>4.11087</v>
+        <v>4.11</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>17.5978</v>
+        <v>17.6</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>2.00141</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1252,22 +1252,22 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>46.5198</v>
+        <v>46.52</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.13987</v>
+        <v>3.14</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>55.0671</v>
+        <v>55.07</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.17913</v>
+        <v>5.18</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>41.9308</v>
+        <v>41.93</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.19276</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="22">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>61.1512</v>
+        <v>61.15</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1.29164</v>
+        <v>1.29</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.6801</v>
+        <v>12.68</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1.06049</v>
+        <v>1.06</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>10.7809</v>
+        <v>10.78</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>1.20791</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="23">
@@ -1328,22 +1328,22 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>68.34520000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.37495</v>
+        <v>1.37</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>13.2087</v>
+        <v>13.21</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1.4056</v>
+        <v>1.41</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>9.66431</v>
+        <v>9.66</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.889279</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="24">
@@ -1366,22 +1366,22 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>60.7893</v>
+        <v>60.79</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2.08809</v>
+        <v>2.09</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>21.6065</v>
+        <v>21.61</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>6.03911</v>
+        <v>6.04</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>17.9722</v>
+        <v>17.97</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>3.59965</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>61.3184</v>
+        <v>61.32</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1.31007</v>
+        <v>1.31</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>13.5507</v>
+        <v>13.55</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1.05291</v>
+        <v>1.05</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>10.4539</v>
+        <v>10.45</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.782338</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="26">
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>63.4365</v>
+        <v>63.44</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1.25653</v>
+        <v>1.26</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>14.6201</v>
+        <v>14.62</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1.41313</v>
+        <v>1.41</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>11.2586</v>
+        <v>11.26</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1.03979</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="27">
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>60.1794</v>
+        <v>60.18</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>1.75561</v>
+        <v>1.76</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>37.6932</v>
+        <v>37.69</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>3.46028</v>
+        <v>3.46</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>16.6243</v>
+        <v>16.62</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1.79671</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="28">
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>59.6653</v>
+        <v>59.67</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2.07727</v>
+        <v>2.08</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>40.4269</v>
+        <v>40.43</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>3.94597</v>
+        <v>3.95</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>22.5329</v>
+        <v>22.53</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>3.06286</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="29">
@@ -1556,22 +1556,22 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>61.1333</v>
+        <v>61.13</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1.47352</v>
+        <v>1.47</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>37.6583</v>
+        <v>37.66</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2.46171</v>
+        <v>2.46</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>15.9209</v>
+        <v>15.92</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1.52742</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="30">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>59.1624</v>
+        <v>59.16</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2.08686</v>
+        <v>2.09</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>16.4201</v>
+        <v>16.42</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1.48065</v>
+        <v>1.48</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>9.65724</v>
+        <v>9.66</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.60671</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="31">
@@ -1632,22 +1632,22 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>58.9509</v>
+        <v>58.95</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3.70695</v>
+        <v>3.71</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32.617</v>
+        <v>32.62</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>13.8725</v>
+        <v>13.87</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.0456</v>
+        <v>19.05</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2.78188</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="32">
@@ -1670,22 +1670,22 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>44.4271</v>
+        <v>44.43</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2.6278</v>
+        <v>2.63</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>63.5251</v>
+        <v>63.53</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>7.79503</v>
+        <v>7.8</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>18.3716</v>
+        <v>18.37</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>2.29613</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>76.86799999999999</v>
+        <v>76.87</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>1.21979</v>
+        <v>1.22</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>12.7994</v>
+        <v>12.8</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2.91995</v>
+        <v>2.92</v>
       </c>
       <c r="J33" s="7" t="n">
         <v>10.19</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>2.54163</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="34">
@@ -1746,22 +1746,22 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>54.8885</v>
+        <v>54.89</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>3.03574</v>
+        <v>3.04</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>37.2382</v>
+        <v>37.24</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>5.10087</v>
+        <v>5.1</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>15.9148</v>
+        <v>15.91</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>2.32286</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="35">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>60.9404</v>
+        <v>60.94</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>2.82634</v>
+        <v>2.83</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>31.3101</v>
+        <v>31.31</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>5.74705</v>
+        <v>5.75</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>13.1379</v>
+        <v>13.14</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>3.73916</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="36">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>46.5754</v>
+        <v>46.58</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2.77748</v>
+        <v>2.78</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>73.78579999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>6.17545</v>
+        <v>6.18</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>37.4098</v>
+        <v>37.41</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>5.80018</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37">
@@ -1860,22 +1860,22 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>39.6119</v>
+        <v>39.61</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>2.86237</v>
+        <v>2.86</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>57.4091</v>
+        <v>57.41</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>5.69278</v>
+        <v>5.69</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>30.1342</v>
+        <v>30.13</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>4.77515</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="38">
@@ -1898,22 +1898,22 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>64.6879</v>
+        <v>64.69</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1.76489</v>
+        <v>1.76</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>12.0013</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1.28003</v>
+        <v>1.28</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>8.075659999999999</v>
+        <v>8.08</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>1.39227</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="39">
@@ -1936,22 +1936,22 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>47.846</v>
+        <v>47.85</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2.47644</v>
+        <v>2.48</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>77.7573</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>6.40062</v>
+        <v>6.4</v>
       </c>
       <c r="J39" s="7" t="n">
         <v>27.12</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>3.51108</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="40">
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>55.6526</v>
+        <v>55.65</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>3.84288</v>
+        <v>3.84</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>27.1033</v>
+        <v>27.1</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>21.354</v>
+        <v>21.35</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>17.4894</v>
+        <v>17.49</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>6.79485</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="41">
@@ -2012,22 +2012,22 @@
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>55.3554</v>
+        <v>55.36</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>2.34464</v>
+        <v>2.34</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>17.8303</v>
+        <v>17.83</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1.69274</v>
+        <v>1.69</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>13.0263</v>
+        <v>13.03</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>1.25874</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="42">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>63.5177</v>
+        <v>63.52</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1.69368</v>
+        <v>1.69</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>17.3502</v>
+        <v>17.35</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1.19179</v>
+        <v>1.19</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>14.0242</v>
+        <v>14.02</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>1.31145</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="43">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>52.1748</v>
+        <v>52.17</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>2.1819</v>
+        <v>2.18</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>91.57389999999999</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>8.96513</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>28.7667</v>
+        <v>28.77</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>4.81046</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="44">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>59.1492</v>
+        <v>59.15</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1.85184</v>
+        <v>1.85</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>12.5413</v>
+        <v>12.54</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1.3529</v>
+        <v>1.35</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>8.07793</v>
+        <v>8.08</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>2.25901</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="45">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>58.5651</v>
+        <v>58.57</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>1.53379</v>
+        <v>1.53</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>13.7783</v>
+        <v>13.78</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>1.14042</v>
+        <v>1.14</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>8.81794</v>
+        <v>8.82</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.886879</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="46">
@@ -2202,22 +2202,22 @@
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>65.624</v>
+        <v>65.62</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1.94953</v>
+        <v>1.95</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>11.2089</v>
+        <v>11.21</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2.24473</v>
+        <v>2.24</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>14.4501</v>
+        <v>14.45</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>4.06306</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="47">
@@ -2240,22 +2240,22 @@
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>77.2261</v>
+        <v>77.23</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3.8868</v>
+        <v>3.89</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>48.8693</v>
+        <v>48.87</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>16.7455</v>
+        <v>16.75</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>20.1113</v>
+        <v>20.11</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>8.17094</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="48">
@@ -2278,22 +2278,22 @@
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>58.333</v>
+        <v>58.33</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>4.09083</v>
+        <v>4.09</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>21.7309</v>
+        <v>21.73</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>3.88796</v>
+        <v>3.89</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>17.2929</v>
+        <v>17.29</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3.0582</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="49">
@@ -2316,22 +2316,22 @@
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>60.6056</v>
+        <v>60.61</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>1.36656</v>
+        <v>1.37</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>12.5977</v>
+        <v>12.6</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1.02186</v>
+        <v>1.02</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>10.2335</v>
+        <v>10.23</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.961419</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="50">
@@ -2354,22 +2354,22 @@
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>59.9331</v>
+        <v>59.93</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>3.75334</v>
+        <v>3.75</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>42.9322</v>
+        <v>42.93</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>17.6435</v>
+        <v>17.64</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>15.8661</v>
+        <v>15.87</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>3.47266</v>
+        <v>3.47</v>
       </c>
     </row>
   </sheetData>
@@ -2387,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2507,7 +2507,7 @@
       <c r="C5" s="9" t="inlineStr"/>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>The structure the prediction was made from, and its only input.</t>
+          <t>Structure; the only input to the prediction.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Spread of the mixture density network's own distribution for that value. The model's estimate of its own confidence, not a DFT or measured error.</t>
+          <t>Spread of the mixture density network's predicted distribution for that value, the model's own uncertainty estimate.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>S0 surface: E_S0 at the T1 geometry minus E_S0 at its own. The model's counterpart to the DFT lambda_S0_T1.</t>
+          <t>S0 surface: E_S0 at the T1 geometry minus E_S0 at its own.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Spread of the mixture density network's own distribution for that value. The model's estimate of its own confidence, not a DFT or measured error.</t>
+          <t>Spread of the mixture density network's predicted distribution for that value, the model's own uncertainty estimate.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>T1 surface: E_T1 at the S0 geometry minus E_T1 at its own. The model's counterpart to the DFT lambda_T1_S0.</t>
+          <t>T1 surface: E_T1 at the S0 geometry minus E_T1 at its own.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Spread of the mixture density network's own distribution for that value. The model's estimate of its own confidence, not a DFT or measured error.</t>
+          <t>Spread of the mixture density network's predicted distribution for that value, the model's own uncertainty estimate.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>network in ml/data/model.pt. Nothing measured and nothing calculated</t>
+          <t>network in ml/data/model.pt. The same three quantities from DFT are in</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -2710,7 +2710,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>enters a value here: the same three quantities from DFT are in</t>
+          <t>quencher_properties_calc.xlsx under the same headers.</t>
         </is>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -2721,7 +2721,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>quencher_properties_calc.xlsx, column for column, and the two files are meant to be</t>
+          <t>Written by computational_data_scripts/quencher_ml.py, which needs the ml extra and</t>
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -2732,7 +2732,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>read side by side rather than merged. The per-atom spin densities and the mixture</t>
+          <t>is not a stage of reproduce.py.</t>
         </is>
       </c>
       <c r="B17" s="9" t="n"/>
@@ -2743,7 +2743,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>parameters the model also returns are not carried.</t>
+          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
       <c r="B18" s="9" t="n"/>
@@ -2751,39 +2751,6 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="9" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Written by computational_data_scripts/quencher_ml.py, which needs the ml extra and</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>is not a stage of reproduce.py.</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="9" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/computational_data_processed/quencher_properties_ml.xlsx
+++ b/data/computational_data_processed/quencher_properties_ml.xlsx
@@ -568,22 +568,22 @@
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>60.09</v>
+        <v>60.58</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1.15</v>
+        <v>0.73</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.03</v>
+        <v>12.62</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="4">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>53.28</v>
+        <v>52.08</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>81.06999999999999</v>
+        <v>94</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>22.7</v>
+        <v>9.06</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>23.17</v>
+        <v>24.39</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>4.56</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>60.72</v>
+        <v>59.62</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>32.46</v>
+        <v>30.75</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>3.09</v>
+        <v>2.22</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>19.18</v>
+        <v>19.07</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="6">
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>67.56999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1.25</v>
+        <v>0.98</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>15.43</v>
+        <v>16.32</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>11.52</v>
+        <v>11.37</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>58.52</v>
+        <v>59.21</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2.62</v>
+        <v>1.12</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>11.79</v>
+        <v>13.02</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1.48</v>
+        <v>0.77</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>10.2</v>
+        <v>11.47</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="8">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60.48</v>
+        <v>60.62</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>13.44</v>
+        <v>13.07</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="9">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.06</v>
+        <v>11.66</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.29</v>
+        <v>0.79</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="10">
@@ -834,22 +834,22 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>47.02</v>
+        <v>49.07</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>58.47</v>
+        <v>59.18</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>5.03</v>
+        <v>4.64</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>31.47</v>
+        <v>33.77</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.58</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="11">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>57.02</v>
+        <v>57.68</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>17.53</v>
+        <v>18.33</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>13.33</v>
+        <v>14.89</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="12">
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>72.2</v>
+        <v>72.84</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2.92</v>
+        <v>1.54</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>28.64</v>
+        <v>24.37</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>8.720000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>13.73</v>
+        <v>16.3</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.81</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>75.59999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.76</v>
+        <v>3.59</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28.87</v>
+        <v>34.17</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>10.59</v>
+        <v>7.14</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>17.34</v>
+        <v>25.57</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>53.33</v>
+        <v>56.61</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3.94</v>
+        <v>1.96</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>21.08</v>
+        <v>16.12</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>5.86</v>
+        <v>2.27</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.27</v>
+        <v>12.83</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3.59</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="15">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>57.05</v>
+        <v>56.89</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>19.05</v>
+        <v>19.52</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>2.98</v>
+        <v>1.52</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>14.48</v>
+        <v>14.91</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>53.83</v>
+        <v>53.99</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2.21</v>
+        <v>1.52</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>91.58</v>
+        <v>95.19</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>29.9</v>
+        <v>30.32</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>5.1</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="17">
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>61.23</v>
+        <v>62.65</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3.06</v>
+        <v>1.89</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>17.14</v>
+        <v>17.42</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>14.11</v>
+        <v>14.5</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1138,22 +1138,22 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>56.78</v>
+        <v>56.22</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>11.03</v>
+        <v>10.64</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="19">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>79.86</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1.92</v>
+        <v>1.15</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19.64</v>
+        <v>15</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>9.789999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>12.62</v>
+        <v>13.84</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>4.02</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="20">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>54.59</v>
+        <v>52.27</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>23.57</v>
+        <v>21.83</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>4.11</v>
+        <v>2.46</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>17.6</v>
+        <v>17.82</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="21">
@@ -1252,22 +1252,22 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>46.52</v>
+        <v>49.85</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>55.07</v>
+        <v>59.37</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.18</v>
+        <v>4.72</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>41.93</v>
+        <v>33.75</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.19</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="22">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>61.15</v>
+        <v>61.1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.68</v>
+        <v>12.09</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>10.78</v>
+        <v>10.63</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>1.21</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="23">
@@ -1328,22 +1328,22 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>68.34999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.37</v>
+        <v>0.99</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>13.21</v>
+        <v>13.35</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1.41</v>
+        <v>0.79</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>9.66</v>
+        <v>10.17</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="24">
@@ -1366,22 +1366,22 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>60.79</v>
+        <v>63.41</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>21.61</v>
+        <v>20.36</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>6.04</v>
+        <v>2.57</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>17.97</v>
+        <v>17.52</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="25">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>61.32</v>
+        <v>60.93</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>13.55</v>
+        <v>12.48</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>10.45</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="26">
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>63.44</v>
+        <v>63.33</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>14.62</v>
+        <v>13.46</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1.41</v>
+        <v>0.87</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>11.26</v>
+        <v>10.98</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>60.18</v>
+        <v>61.53</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>37.69</v>
+        <v>38.85</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>3.46</v>
+        <v>2.67</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>16.62</v>
+        <v>17.26</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="28">
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>59.67</v>
+        <v>60.82</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>40.43</v>
+        <v>43.12</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>3.95</v>
+        <v>3.71</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>22.53</v>
+        <v>22.1</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>3.06</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="29">
@@ -1556,22 +1556,22 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>61.13</v>
+        <v>59.21</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>37.66</v>
+        <v>36.69</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>15.92</v>
+        <v>15.55</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="30">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>59.16</v>
+        <v>57.53</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>16.42</v>
+        <v>14.75</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>9.66</v>
+        <v>8.91</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="31">
@@ -1632,22 +1632,22 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>58.95</v>
+        <v>59.85</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3.71</v>
+        <v>2.47</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32.62</v>
+        <v>26.44</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>13.87</v>
+        <v>5.76</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.05</v>
+        <v>19.83</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2.78</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="32">
@@ -1670,22 +1670,22 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>44.43</v>
+        <v>43.94</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>63.53</v>
+        <v>65.23</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>18.37</v>
+        <v>18.81</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>76.87</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>12.8</v>
+        <v>15.51</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>10.19</v>
+        <v>10.9</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>2.54</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="34">
@@ -1746,22 +1746,22 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>54.89</v>
+        <v>53.68</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>3.04</v>
+        <v>2.12</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>37.24</v>
+        <v>35.54</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>5.1</v>
+        <v>4.31</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>15.91</v>
+        <v>15.14</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="35">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>60.94</v>
+        <v>59.1</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>31.31</v>
+        <v>29.5</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>5.75</v>
+        <v>7.86</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>13.14</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>3.74</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="36">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>73.79000000000001</v>
+        <v>69.58</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>6.18</v>
+        <v>4.55</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>37.41</v>
+        <v>37.52</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>5.8</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="37">
@@ -1860,22 +1860,22 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>39.61</v>
+        <v>38.94</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>57.41</v>
+        <v>58.81</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>5.69</v>
+        <v>4.06</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>30.13</v>
+        <v>31.72</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>4.78</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="38">
@@ -1898,22 +1898,22 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>64.69</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>12</v>
+        <v>11.42</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1.28</v>
+        <v>0.84</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>8.08</v>
+        <v>7.24</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="39">
@@ -1936,22 +1936,22 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>47.85</v>
+        <v>49.05</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>77.76000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>6.4</v>
+        <v>8.01</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>27.12</v>
+        <v>27.49</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>3.51</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="40">
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>55.65</v>
+        <v>56.32</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>3.84</v>
+        <v>3.01</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>21.35</v>
+        <v>6.79</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>17.49</v>
+        <v>15.33</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>6.79</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="41">
@@ -2012,22 +2012,22 @@
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>55.36</v>
+        <v>55.67</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>17.83</v>
+        <v>17.45</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>13.03</v>
+        <v>13.6</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="42">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>63.52</v>
+        <v>64.03</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>17.35</v>
+        <v>17.51</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1.19</v>
+        <v>0.82</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>14.02</v>
+        <v>14.78</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="43">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>52.17</v>
+        <v>51.51</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>2.18</v>
+        <v>1.71</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>91.56999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>8.970000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>28.77</v>
+        <v>26.8</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="44">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>59.15</v>
+        <v>59.38</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>12.54</v>
+        <v>11.59</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>8.08</v>
+        <v>7.08</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="45">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>58.57</v>
+        <v>59.42</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>13.78</v>
+        <v>13.46</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46">
@@ -2202,22 +2202,22 @@
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>65.62</v>
+        <v>65.59</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>11.21</v>
+        <v>10.34</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>14.45</v>
+        <v>16.15</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="47">
@@ -2240,22 +2240,22 @@
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>77.23</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3.89</v>
+        <v>6.63</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>48.87</v>
+        <v>19.67</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>16.75</v>
+        <v>15.86</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>20.11</v>
+        <v>11.67</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>8.17</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="48">
@@ -2278,22 +2278,22 @@
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>58.33</v>
+        <v>63</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>4.09</v>
+        <v>3</v>
       </c>
       <c r="H48" s="7" t="n">
         <v>21.73</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>3.89</v>
+        <v>2.98</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>17.29</v>
+        <v>18.53</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3.06</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="49">
@@ -2316,22 +2316,22 @@
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>60.61</v>
+        <v>61.53</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>12.6</v>
+        <v>12.22</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>10.23</v>
+        <v>10.16</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2354,22 +2354,22 @@
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>59.93</v>
+        <v>64.5</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>3.75</v>
+        <v>1.88</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>42.93</v>
+        <v>14.32</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>17.64</v>
+        <v>10.57</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>15.87</v>
+        <v>12.34</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>3.47</v>
+        <v>4.81</v>
       </c>
     </row>
   </sheetData>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: triplet_energy_adiabatic</t>
+          <t>ml/data/model_final.pt: triplet_energy_adiabatic</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: triplet_energy_adiabatic_uncertainty</t>
+          <t>ml/data/model_final.pt: triplet_energy_adiabatic_uncertainty</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: lamda_S_T</t>
+          <t>ml/data/model_final.pt: lamda_S_T</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: lamda_S_T_uncertainty</t>
+          <t>ml/data/model_final.pt: lamda_S_T_uncertainty</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: lamda_T_S</t>
+          <t>ml/data/model_final.pt: lamda_T_S</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>ml/data/model.pt: lamda_T_S_uncertainty</t>
+          <t>ml/data/model_final.pt: lamda_T_S_uncertainty</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>network in ml/data/model.pt. The same three quantities from DFT are in</t>
+          <t>network in ml/data/model_final.pt. The same three quantities from DFT are in</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
